--- a/src/main/resources/public/BCKCHT_163.xlsx
+++ b/src/main/resources/public/BCKCHT_163.xlsx
@@ -124,7 +124,7 @@
     <t>NĂNG LỰC THÔNG QUA BẾN CẢNG, CẦU CẢNG</t>
   </si>
   <si>
-    <t>Danh mục bến cảng, cầu cảng</t>
+    <t>Danh mục bến cảng, cầu cảng, cảng bến thủy nội địa</t>
   </si>
   <si>
     <t>A</t>
@@ -154,10 +154,10 @@
     <t>Chiều dài bến cảng, cầu cảng (m)</t>
   </si>
   <si>
-    <t>Tổng diện tích (ha)</t>
-  </si>
-  <si>
     <t>Tàu neo đậu, làm hàng lớn nhất (DWT)</t>
+  </si>
+  <si>
+    <t>Ghi chú</t>
   </si>
   <si>
     <t>(Ký, ghi rõ họ tên)</t>
@@ -754,7 +754,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" mc:Ignorable="x14ac">
+<worksheet xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>

--- a/src/main/resources/public/BCKCHT_163.xlsx
+++ b/src/main/resources/public/BCKCHT_163.xlsx
@@ -1,24 +1,42 @@
 
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
-  <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
-  </bookViews>
-  <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-  </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
-</workbook>
+<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <Application>Microsoft Excel</Application>
+  <DocSecurity>0</DocSecurity>
+  <ScaleCrop>false</ScaleCrop>
+  <HeadingPairs>
+    <vt:vector size="2" baseType="variant">
+      <vt:variant>
+        <vt:lpstr>Worksheets</vt:lpstr>
+      </vt:variant>
+      <vt:variant>
+        <vt:i4>1</vt:i4>
+      </vt:variant>
+    </vt:vector>
+  </HeadingPairs>
+  <TitlesOfParts>
+    <vt:vector size="1" baseType="lpstr">
+      <vt:lpstr>Sheet1</vt:lpstr>
+    </vt:vector>
+  </TitlesOfParts>
+  <Company/>
+  <LinksUpToDate>false</LinksUpToDate>
+  <SharedDoc>false</SharedDoc>
+  <HyperlinksChanged>false</HyperlinksChanged>
+  <AppVersion>16.0300</AppVersion>
+</Properties>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
+<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:dcmitype="http://purl.org/dc/dcmitype/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <dc:creator/>
+  <cp:lastModifiedBy/>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2015-06-05T18:17:20Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2025-11-17T09:01:57Z</dcterms:modified>
+</cp:coreProperties>
+</file>
+
+<file path=xl\comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Author</author>
@@ -100,7 +118,7 @@
 </comments>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
   <si>
     <t>STT</t>
@@ -121,7 +139,7 @@
     <t>Ngày 01 tháng 3 hàng năm</t>
   </si>
   <si>
-    <t>NĂNG LỰC THÔNG QUA BẾN CẢNG, CẦU CẢNG</t>
+    <t>NĂNG LỰC THÔNG QUA CẢNG BIỂN, CẦU CẢNG, CẢNG BẾN THỦY NỔI ĐỊA</t>
   </si>
   <si>
     <t>Danh mục bến cảng, cầu cảng, cảng bến thủy nội địa</t>
@@ -258,7 +276,7 @@
 </sst>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -492,7 +510,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -753,7 +771,26 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+  </sheets>
+  <calcPr calcId="162913"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+  </extLst>
+</workbook>
+</file>
+
+<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
